--- a/glossry_template.xlsx
+++ b/glossry_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vidvan/Projects/datahive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7526B5B7-37B2-0A43-8690-A60BD968A47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3774F5-B284-FA42-A79E-B3F426A033A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3980" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{28C07E68-7A6F-784E-8597-FFAA0B728F80}"/>
+    <workbookView xWindow="1300" yWindow="2780" windowWidth="30720" windowHeight="17180" xr2:uid="{28C07E68-7A6F-784E-8597-FFAA0B728F80}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="52">
   <si>
     <t>database</t>
   </si>
@@ -56,9 +56,6 @@
     <t>connection</t>
   </si>
   <si>
-    <t>postgres</t>
-  </si>
-  <si>
     <t>business_name</t>
   </si>
   <si>
@@ -83,37 +80,121 @@
     <t>steward</t>
   </si>
   <si>
-    <t>datahivepoc</t>
-  </si>
-  <si>
-    <t>test_customer_tbl</t>
-  </si>
-  <si>
-    <t>customer_nm</t>
-  </si>
-  <si>
-    <t>customer name</t>
-  </si>
-  <si>
-    <t>Name of the customer</t>
-  </si>
-  <si>
     <t>PII</t>
   </si>
   <si>
     <t>Confidential</t>
   </si>
   <si>
-    <t>Workday</t>
-  </si>
-  <si>
     <t>Sales</t>
   </si>
   <si>
-    <t>Sales Data Steward</t>
-  </si>
-  <si>
-    <t>dhpoc-bronze</t>
+    <t>Snowflake</t>
+  </si>
+  <si>
+    <t>SALES_DB</t>
+  </si>
+  <si>
+    <t>RAW</t>
+  </si>
+  <si>
+    <t>DH_POC_CUTOMER_TBL</t>
+  </si>
+  <si>
+    <t>CUSTOMER_ID</t>
+  </si>
+  <si>
+    <t>FIRST_NAME</t>
+  </si>
+  <si>
+    <t>LAST_NAME</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>PHONE</t>
+  </si>
+  <si>
+    <t>ADDRESS_LINE</t>
+  </si>
+  <si>
+    <t>CITY</t>
+  </si>
+  <si>
+    <t>STATE</t>
+  </si>
+  <si>
+    <t>ZIP</t>
+  </si>
+  <si>
+    <t>PREFERRED_STORE_ID</t>
+  </si>
+  <si>
+    <t>PREFERRED_CHANNEL</t>
+  </si>
+  <si>
+    <t>MARKETING_OPT_IN</t>
+  </si>
+  <si>
+    <t>CREATED_AT</t>
+  </si>
+  <si>
+    <t>Customer ID</t>
+  </si>
+  <si>
+    <t>Identification of a customer</t>
+  </si>
+  <si>
+    <t>Identification of a customer to the pizza shop</t>
+  </si>
+  <si>
+    <t>Pzaap</t>
+  </si>
+  <si>
+    <t>Sales Steward</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Laste Name</t>
+  </si>
+  <si>
+    <t>Email Address</t>
+  </si>
+  <si>
+    <t>Mibile Number</t>
+  </si>
+  <si>
+    <t>Address First Line</t>
+  </si>
+  <si>
+    <t>Cty</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Postal Code</t>
+  </si>
+  <si>
+    <t>Pizza shop identification number</t>
+  </si>
+  <si>
+    <t>Mode of communication</t>
+  </si>
+  <si>
+    <t>Marketing Source</t>
+  </si>
+  <si>
+    <t>Hwowmdid custimer come to know this shop/brand</t>
+  </si>
+  <si>
+    <t>Created date time</t>
+  </si>
+  <si>
+    <t>Public</t>
   </si>
 </sst>
 </file>
@@ -505,22 +586,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1711D7D8-0DB8-2849-AE69-CD935E21422E}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -540,66 +621,534 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
-      </c>
-      <c r="M1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="K2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" t="s">
+        <v>51</v>
+      </c>
+      <c r="K10" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" t="s">
+        <v>51</v>
+      </c>
+      <c r="K11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" t="s">
+        <v>15</v>
+      </c>
+      <c r="M13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14" t="s">
+        <v>51</v>
+      </c>
+      <c r="K14" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" t="s">
+        <v>15</v>
+      </c>
+      <c r="M14" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
